--- a/1. Reporting_Data/IB_Daily Ticker/processed/2026/202608/Ticker_20260812.xlsx
+++ b/1. Reporting_Data/IB_Daily Ticker/processed/2026/202608/Ticker_20260812.xlsx
@@ -46,9 +46,6 @@
     <t>006800.KS</t>
   </si>
   <si>
-    <t>011200</t>
-  </si>
-  <si>
     <t>017800.KS</t>
   </si>
   <si>
@@ -70,6 +67,9 @@
     <t>1109</t>
   </si>
   <si>
+    <t>11200</t>
+  </si>
+  <si>
     <t>1258</t>
   </si>
   <si>
@@ -460,9 +460,6 @@
     <t>006800.KS  Equity</t>
   </si>
   <si>
-    <t>011200  Equity</t>
-  </si>
-  <si>
     <t>017800.KS  Equity</t>
   </si>
   <si>
@@ -482,6 +479,9 @@
   </si>
   <si>
     <t>1109 HK Equity</t>
+  </si>
+  <si>
+    <t>11200  Equity</t>
   </si>
   <si>
     <t>1258 HK Equity</t>
@@ -1394,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
         <v>134</v>
@@ -1414,7 +1414,7 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
         <v>134</v>

--- a/1. Reporting_Data/IB_Daily Ticker/processed/2026/202608/Ticker_20260812.xlsx
+++ b/1. Reporting_Data/IB_Daily Ticker/processed/2026/202608/Ticker_20260812.xlsx
@@ -46,6 +46,9 @@
     <t>006800.KS</t>
   </si>
   <si>
+    <t>011200</t>
+  </si>
+  <si>
     <t>017800.KS</t>
   </si>
   <si>
@@ -67,9 +70,6 @@
     <t>1109</t>
   </si>
   <si>
-    <t>11200</t>
-  </si>
-  <si>
     <t>1258</t>
   </si>
   <si>
@@ -460,6 +460,9 @@
     <t>006800.KS  Equity</t>
   </si>
   <si>
+    <t>011200  Equity</t>
+  </si>
+  <si>
     <t>017800.KS  Equity</t>
   </si>
   <si>
@@ -479,9 +482,6 @@
   </si>
   <si>
     <t>1109 HK Equity</t>
-  </si>
-  <si>
-    <t>11200  Equity</t>
   </si>
   <si>
     <t>1258 HK Equity</t>
@@ -1394,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" t="s">
         <v>134</v>
@@ -1414,7 +1414,7 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s">
         <v>134</v>
